--- a/output/pdf_financials_xlsx/TRR.xlsx
+++ b/output/pdf_financials_xlsx/TRR.xlsx
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.63148</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.013133</v>
       </c>
     </row>
     <row r="93">
@@ -2628,7 +2628,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.63148</v>
       </c>

--- a/output/pdf_financials_xlsx/TRR.xlsx
+++ b/output/pdf_financials_xlsx/TRR.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.035362</v>
       </c>
     </row>
     <row r="13">
@@ -797,7 +797,7 @@
         <v>-0.678051</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.27852</v>
+        <v>-4.313882</v>
       </c>
     </row>
     <row r="28">
@@ -823,7 +823,7 @@
         <v>-0.6530860000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.250321</v>
+        <v>-4.285683</v>
       </c>
     </row>
     <row r="30">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032017</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032017</v>
       </c>
     </row>
     <row r="125">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032017</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032017</v>
       </c>
     </row>
     <row r="126">
@@ -3164,7 +3164,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-0.032017</v>
       </c>
@@ -3734,7 +3738,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/output/pdf_financials_xlsx/TRR.xlsx
+++ b/output/pdf_financials_xlsx/TRR.xlsx
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.025128</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.023102</v>
       </c>
     </row>
     <row r="71">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.025128</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.023102</v>
       </c>
     </row>
     <row r="72">
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.025128</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.023102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1488,15 +1488,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.003106173581800849</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.001837705367671531</v>
       </c>
     </row>
     <row r="81">
@@ -1877,10 +1873,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>-0.010251</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.016121</v>
       </c>
     </row>
     <row r="111">
@@ -2532,7 +2528,11 @@
           <t>Lease liabilities (Note 6)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.025128</v>
       </c>
@@ -2764,7 +2764,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-0.010251</v>
       </c>
@@ -3108,7 +3112,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
